--- a/data/trans_orig/P70C2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70C2_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le es dificil cumplir con las obligaciones familiares debido al tiempo que paso en el trabajo en 2023</t>
+          <t>Población según si le es dificil cumplir con las obligaciones familiares debido al tiempo que paso en el trabajo en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27618</t>
+          <t>27927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58849</t>
+          <t>58998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44433</t>
+          <t>44323</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64037</t>
+          <t>65036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79212</t>
+          <t>78394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116467</t>
+          <t>116185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,49%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38223</t>
+          <t>36524</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,82 +858,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>41,31%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>13863</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22806</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>28,07%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>37102</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>23183</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>52365</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>21,87%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>13,67%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>43,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13863</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7311</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23102</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>17,06%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>28,44%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>37102</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>23596</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>54159</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>13,91%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32446</t>
+          <t>29858</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35124</t>
+          <t>35245</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20577</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23322</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21401</t>
+          <t>21223</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -1295,97 +1295,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3596</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2727</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>3157</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151692</t>
+          <t>153351</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>198658</t>
+          <t>198986</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>174848</t>
+          <t>176554</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>279999</t>
+          <t>288610</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>345205</t>
+          <t>347492</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>483135</t>
+          <t>480495</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54846</t>
+          <t>57813</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92374</t>
+          <t>93831</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34182</t>
+          <t>33643</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90290</t>
+          <t>89478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98529</t>
+          <t>98948</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>167823</t>
+          <t>167132</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22148</t>
+          <t>21291</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50145</t>
+          <t>50463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32176</t>
+          <t>31742</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37227</t>
+          <t>36415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75254</t>
+          <t>75332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27719</t>
+          <t>28984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60735</t>
+          <t>63135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11698</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36616</t>
+          <t>36519</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>43428</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90809</t>
+          <t>88258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30096</t>
+          <t>30757</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33441</t>
+          <t>33630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>22517</t>
+          <t>22008</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>53057</t>
+          <t>53344</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>12417</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>22725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>204459</t>
+          <t>204848</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>251477</t>
+          <t>250652</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>141082</t>
+          <t>140981</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>170189</t>
+          <t>171558</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>353937</t>
+          <t>354397</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>409072</t>
+          <t>410607</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85153</t>
+          <t>84376</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>121238</t>
+          <t>121735</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78677</t>
+          <t>78879</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106168</t>
+          <t>104494</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>171567</t>
+          <t>171106</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>217104</t>
+          <t>215325</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>27370</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52258</t>
+          <t>53811</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>21657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39106</t>
+          <t>38308</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55492</t>
+          <t>54984</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84393</t>
+          <t>84656</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39836</t>
+          <t>41507</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69474</t>
+          <t>70165</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30393</t>
+          <t>30004</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50558</t>
+          <t>49344</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>76021</t>
+          <t>76699</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>111866</t>
+          <t>112285</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>15560</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35257</t>
+          <t>35570</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>20202</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>38181</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40497</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66521</t>
+          <t>65401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15294</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34265</t>
+          <t>34832</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>376078</t>
+          <t>378096</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>652649</t>
+          <t>643360</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>218348</t>
+          <t>217294</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>294807</t>
+          <t>291136</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>610516</t>
+          <t>614508</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>966736</t>
+          <t>929078</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46854</t>
+          <t>51649</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>191604</t>
+          <t>187333</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67407</t>
+          <t>67374</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>102198</t>
+          <t>101466</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>110600</t>
+          <t>124091</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>278140</t>
+          <t>272475</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56428</t>
+          <t>56835</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>30702</t>
+          <t>31653</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>53035</t>
+          <t>52814</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>37418</t>
+          <t>41325</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>103590</t>
+          <t>103825</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>15224</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>64094</t>
+          <t>64791</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26678</t>
+          <t>26586</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47671</t>
+          <t>47611</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37354</t>
+          <t>44428</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>103253</t>
+          <t>103000</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>51012</t>
+          <t>51425</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35974</t>
+          <t>36810</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29865</t>
+          <t>29100</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>80049</t>
+          <t>80081</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31312</t>
+          <t>32644</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41213</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>17711</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>56322</t>
+          <t>55563</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>128456</t>
+          <t>127246</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>161120</t>
+          <t>161035</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>86150</t>
+          <t>86199</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>107338</t>
+          <t>107048</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>221482</t>
+          <t>222330</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>259418</t>
+          <t>262352</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,79%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>62955</t>
+          <t>62510</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>91059</t>
+          <t>91556</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>47414</t>
+          <t>46870</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>65600</t>
+          <t>65061</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>115826</t>
+          <t>114587</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>146825</t>
+          <t>147360</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>35922</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23108</t>
+          <t>23715</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32064</t>
+          <t>32565</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55014</t>
+          <t>55424</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17042</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>34139</t>
+          <t>34230</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>15098</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>27701</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>35870</t>
+          <t>34918</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>58023</t>
+          <t>57672</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27843</t>
+          <t>27570</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15975</t>
+          <t>15527</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>38966</t>
+          <t>38317</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18866</t>
+          <t>19415</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>11939</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>26634</t>
+          <t>26154</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>13833</t>
+          <t>13720</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>15389</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>24205</t>
+          <t>24218</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,8%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12111</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -4931,97 +4931,97 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>1153</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2923</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>16,46%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
         <is>
           <t>941</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="S41" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>3457</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>3134</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>19,48%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>3375</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>423</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>421</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -5270,97 +5270,97 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>1153</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>16,92%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="R44" s="2" t="inlineStr">
         <is>
           <t>1004</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="S44" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>3170</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>3493</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>3510</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -5500,97 +5500,97 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
           <t>1598</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="W46" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -5613,97 +5613,97 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="W47" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5726,97 +5726,97 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="W48" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5839,97 +5839,97 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O49" s="2" t="inlineStr">
+      <c r="W49" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W49" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5952,97 +5952,97 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="V50" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="W50" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -6065,97 +6065,97 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="V51" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O51" s="2" t="inlineStr">
+      <c r="W51" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W51" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>973435</t>
+          <t>968866</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1360166</t>
+          <t>1379152</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>714590</t>
+          <t>721708</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>885552</t>
+          <t>883061</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1730046</t>
+          <t>1735249</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2220712</t>
+          <t>2259673</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>273837</t>
+          <t>265924</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>470372</t>
+          <t>473770</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>263452</t>
+          <t>269935</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>352211</t>
+          <t>349112</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>562213</t>
+          <t>559840</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>801082</t>
+          <t>796708</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>97524</t>
+          <t>97858</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>183324</t>
+          <t>185073</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>93200</t>
+          <t>91080</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>133419</t>
+          <t>130862</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>202450</t>
+          <t>204806</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>300691</t>
+          <t>302277</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>115533</t>
+          <t>112826</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>203532</t>
+          <t>204619</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>101871</t>
+          <t>99311</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>146165</t>
+          <t>146653</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>230262</t>
+          <t>228472</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>331668</t>
+          <t>334671</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>58064</t>
+          <t>61214</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>116220</t>
+          <t>119010</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>75702</t>
+          <t>72915</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>114303</t>
+          <t>112522</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>144085</t>
+          <t>146876</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>218736</t>
+          <t>216496</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>31410</t>
+          <t>31632</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>67931</t>
+          <t>69061</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>29763</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>59380</t>
+          <t>63149</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6910,47 +6910,47 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>90205</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>66438</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>116558</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>90205</t>
-        </is>
-      </c>
-      <c r="S58" s="2" t="inlineStr">
-        <is>
-          <t>66396</t>
-        </is>
-      </c>
-      <c r="T58" s="2" t="inlineStr">
-        <is>
-          <t>118320</t>
-        </is>
-      </c>
-      <c r="U58" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="V58" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70C2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70C2_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>43771</t>
+          <t>52639</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27927</t>
+          <t>36771</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58998</t>
+          <t>67670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54703</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44323</t>
+          <t>48578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65036</t>
+          <t>71811</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>98474</t>
+          <t>113282</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78394</t>
+          <t>89728</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116185</t>
+          <t>132016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,0%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>26222</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10860</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36524</t>
+          <t>41900</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>17448</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>28111</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>37102</t>
+          <t>43670</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>29676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>62466</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29858</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>9429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24563</t>
+          <t>20569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10328</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>18940</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21223</t>
+          <t>21862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88409</t>
+          <t>102388</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88409</t>
+          <t>102388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88409</t>
+          <t>102388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>169647</t>
+          <t>194131</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169647</t>
+          <t>194131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>169647</t>
+          <t>194131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>176640</t>
+          <t>192927</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153351</t>
+          <t>166838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>198986</t>
+          <t>218082</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>216923</t>
+          <t>168209</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176554</t>
+          <t>149514</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288610</t>
+          <t>186160</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>393563</t>
+          <t>361136</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>347492</t>
+          <t>329705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>480495</t>
+          <t>392438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73725</t>
+          <t>87531</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57813</t>
+          <t>69122</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93831</t>
+          <t>110921</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>66014</t>
+          <t>72312</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33643</t>
+          <t>57558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89478</t>
+          <t>86360</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>139739</t>
+          <t>159843</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98948</t>
+          <t>136187</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>167132</t>
+          <t>184961</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34420</t>
+          <t>39446</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>25367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50463</t>
+          <t>56080</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>24113</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10263</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31742</t>
+          <t>34462</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>55256</t>
+          <t>63559</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36415</t>
+          <t>47349</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75332</t>
+          <t>84917</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>42407</t>
+          <t>47106</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28984</t>
+          <t>31729</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63135</t>
+          <t>67074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23587</t>
+          <t>26592</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36519</t>
+          <t>37772</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>65993</t>
+          <t>73698</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43428</t>
+          <t>55919</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88258</t>
+          <t>96023</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30757</t>
+          <t>33010</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20723</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33630</t>
+          <t>32456</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>36169</t>
+          <t>39196</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>22008</t>
+          <t>26352</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>53344</t>
+          <t>57971</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>23756</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12417</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12538</t>
+          <t>17693</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>31811</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>703258</t>
+          <t>715125</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>703258</t>
+          <t>715125</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>703258</t>
+          <t>715125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>227540</t>
+          <t>267404</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>204848</t>
+          <t>241817</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>250652</t>
+          <t>291113</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>154872</t>
+          <t>175160</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>140981</t>
+          <t>158781</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>171558</t>
+          <t>192617</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>382412</t>
+          <t>442564</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>354397</t>
+          <t>412162</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>410607</t>
+          <t>476138</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>101662</t>
+          <t>120797</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84376</t>
+          <t>100898</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>121735</t>
+          <t>141244</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91110</t>
+          <t>102552</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78879</t>
+          <t>88557</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104494</t>
+          <t>116737</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>192771</t>
+          <t>223350</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>171106</t>
+          <t>199500</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>215325</t>
+          <t>248159</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>39954</t>
+          <t>46669</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27370</t>
+          <t>34852</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53811</t>
+          <t>62366</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28957</t>
+          <t>32022</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21657</t>
+          <t>23347</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>41777</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>68911</t>
+          <t>78691</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54984</t>
+          <t>64082</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84656</t>
+          <t>97616</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54360</t>
+          <t>59795</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41507</t>
+          <t>45242</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70165</t>
+          <t>76716</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38985</t>
+          <t>42538</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30004</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49344</t>
+          <t>53931</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>93345</t>
+          <t>102334</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>76699</t>
+          <t>84874</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>112285</t>
+          <t>121642</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>24048</t>
+          <t>25193</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>16656</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35570</t>
+          <t>36012</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>28171</t>
+          <t>34472</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20202</t>
+          <t>25059</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38181</t>
+          <t>46337</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>52219</t>
+          <t>59665</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>45469</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65401</t>
+          <t>75129</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>18387</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23332</t>
+          <t>30682</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>17084</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>23456</t>
+          <t>29116</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34832</t>
+          <t>42649</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>461983</t>
+          <t>538246</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>461983</t>
+          <t>538246</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>461983</t>
+          <t>538246</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>351132</t>
+          <t>397474</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>351132</t>
+          <t>397474</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>351132</t>
+          <t>397474</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>813115</t>
+          <t>935720</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>813115</t>
+          <t>935720</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>813115</t>
+          <t>935720</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>505177</t>
+          <t>286590</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>378096</t>
+          <t>262437</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>643360</t>
+          <t>310725</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>241382</t>
+          <t>226527</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>217294</t>
+          <t>210058</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>291136</t>
+          <t>243062</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>746559</t>
+          <t>513117</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>614508</t>
+          <t>485109</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>929078</t>
+          <t>542076</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>54,19%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>121204</t>
+          <t>129743</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51649</t>
+          <t>111573</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>187333</t>
+          <t>152163</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>87302</t>
+          <t>96671</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67374</t>
+          <t>82995</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>101466</t>
+          <t>111409</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>208506</t>
+          <t>226414</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>124091</t>
+          <t>203324</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>272475</t>
+          <t>251496</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>34072</t>
+          <t>35931</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>25454</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56835</t>
+          <t>49463</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42099</t>
+          <t>46971</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31653</t>
+          <t>38238</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>52814</t>
+          <t>60788</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>76172</t>
+          <t>82902</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>41325</t>
+          <t>66857</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>103825</t>
+          <t>99522</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>39152</t>
+          <t>41576</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15224</t>
+          <t>30029</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>64791</t>
+          <t>55080</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>36389</t>
+          <t>39966</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26586</t>
+          <t>30707</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47611</t>
+          <t>50951</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>75542</t>
+          <t>81541</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>44428</t>
+          <t>66339</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>103000</t>
+          <t>97786</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>30844</t>
+          <t>33668</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>22960</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>51425</t>
+          <t>46987</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>27095</t>
+          <t>28934</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19208</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36810</t>
+          <t>37951</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>57939</t>
+          <t>62603</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29100</t>
+          <t>47817</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>80081</t>
+          <t>77722</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>17208</t>
+          <t>18565</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32644</t>
+          <t>28976</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>22454</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>35070</t>
+          <t>33677</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17711</t>
+          <t>24059</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55563</t>
+          <t>46164</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>747657</t>
+          <t>546073</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>747657</t>
+          <t>546073</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>747657</t>
+          <t>546073</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>452130</t>
+          <t>454182</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>452130</t>
+          <t>454182</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>452130</t>
+          <t>454182</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1199787</t>
+          <t>1000254</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1199787</t>
+          <t>1000254</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1199787</t>
+          <t>1000254</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>144051</t>
+          <t>163467</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>127246</t>
+          <t>144597</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>161035</t>
+          <t>179756</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>97048</t>
+          <t>111502</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>100320</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>107048</t>
+          <t>122606</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>241099</t>
+          <t>274969</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>222330</t>
+          <t>254353</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>262352</t>
+          <t>295478</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>75830</t>
+          <t>81247</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>62510</t>
+          <t>67283</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>91556</t>
+          <t>96324</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>55676</t>
+          <t>60316</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>46870</t>
+          <t>50688</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>65061</t>
+          <t>70213</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>131507</t>
+          <t>141563</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>114587</t>
+          <t>124717</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>147360</t>
+          <t>160682</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>25960</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>35922</t>
+          <t>37158</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>16654</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23715</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>42060</t>
+          <t>43955</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32565</t>
+          <t>33568</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55424</t>
+          <t>56281</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>26324</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>18249</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>20984</t>
+          <t>23510</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>28549</t>
+          <t>31558</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>45184</t>
+          <t>49834</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>34918</t>
+          <t>38901</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>57672</t>
+          <t>62712</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>18440</t>
+          <t>19641</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>12707</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27570</t>
+          <t>29483</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15527</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>28601</t>
+          <t>31470</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>22756</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>38317</t>
+          <t>42952</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19415</t>
+          <t>19278</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12708</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>18136</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>27817</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>298819</t>
+          <t>327778</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>298819</t>
+          <t>327778</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>298819</t>
+          <t>327778</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>207767</t>
+          <t>232843</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>207767</t>
+          <t>232843</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>207767</t>
+          <t>232843</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>506586</t>
+          <t>560621</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>506586</t>
+          <t>560621</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>506586</t>
+          <t>560621</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>11296</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>13720</t>
+          <t>14720</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>19879</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>15389</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>24218</t>
+          <t>26356</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>67,78%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>975</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>975</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>457</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>698</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>435</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -6173,17 +6173,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1109519</t>
+          <t>976139</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>968866</t>
+          <t>927042</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1379152</t>
+          <t>1021654</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6325,32 +6325,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>774064</t>
+          <t>752290</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>721708</t>
+          <t>715871</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>883061</t>
+          <t>789502</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>1883584</t>
+          <t>1728429</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1735249</t>
+          <t>1668072</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2259673</t>
+          <t>1789019</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>51,91%</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6403,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>399600</t>
+          <t>450975</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>265924</t>
+          <t>412655</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>473770</t>
+          <t>497366</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6438,32 +6438,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>318053</t>
+          <t>354006</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>269935</t>
+          <t>323512</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>349112</t>
+          <t>382697</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>717653</t>
+          <t>804981</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>559840</t>
+          <t>757316</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>796708</t>
+          <t>857776</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -6516,32 +6516,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>147073</t>
+          <t>163774</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>97858</t>
+          <t>135920</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>185073</t>
+          <t>194477</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>113146</t>
+          <t>125988</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>91080</t>
+          <t>108817</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>130862</t>
+          <t>145936</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>260219</t>
+          <t>289762</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>204806</t>
+          <t>258054</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>302277</t>
+          <t>326101</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>166908</t>
+          <t>181078</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>112826</t>
+          <t>155075</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>204619</t>
+          <t>213610</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,32 +6664,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>124273</t>
+          <t>136996</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>99311</t>
+          <t>118215</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>146653</t>
+          <t>157072</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>291181</t>
+          <t>318074</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>228472</t>
+          <t>286651</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>334671</t>
+          <t>356925</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>92429</t>
+          <t>99594</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>61214</t>
+          <t>80100</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>119010</t>
+          <t>124873</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>93416</t>
+          <t>105357</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>72915</t>
+          <t>86200</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>125254</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>185845</t>
+          <t>204951</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>146876</t>
+          <t>176572</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>216496</t>
+          <t>232658</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>59829</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>31632</t>
+          <t>44515</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>69061</t>
+          <t>78461</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>39982</t>
+          <t>40529</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>29763</t>
+          <t>29934</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>63149</t>
+          <t>52355</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>90205</t>
+          <t>100357</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>66438</t>
+          <t>82215</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>116558</t>
+          <t>125061</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -6968,17 +6968,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>1965751</t>
+          <t>1931388</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1965751</t>
+          <t>1931388</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1965751</t>
+          <t>1931388</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>1462935</t>
+          <t>1515166</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1462935</t>
+          <t>1515166</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>1462935</t>
+          <t>1515166</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>3428686</t>
+          <t>3446554</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>3428686</t>
+          <t>3446554</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3428686</t>
+          <t>3446554</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
